--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -1,120 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAFBC4C-B2C9-7E4B-BEEA-F2BE981EE48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="26360" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>area_type</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>periurban</t>
-  </si>
-  <si>
-    <t>rural</t>
-  </si>
-  <si>
-    <t>urban</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -214,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -248,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -283,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -459,81 +350,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>area_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C2">
-        <v>36806.307999999997</v>
+        <v>35744.549</v>
       </c>
       <c r="D2">
-        <v>34220.326999999997</v>
+        <v>33238.17</v>
       </c>
       <c r="E2">
-        <v>39394.160000000003</v>
+        <v>38248.26</v>
       </c>
       <c r="F2">
-        <v>341516.82299999997</v>
+        <v>331345.192</v>
       </c>
       <c r="G2">
-        <v>326940.01</v>
+        <v>317122.593</v>
       </c>
       <c r="H2">
-        <v>356098.20199999999</v>
+        <v>345603.421</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -545,39 +465,43 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45422491789.039001</v>
+        <v>44069681090.952</v>
       </c>
       <c r="M2">
-        <v>43480886742.723</v>
+        <v>42168739942.258</v>
       </c>
       <c r="N2">
-        <v>47365394777.025002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+        <v>45964704339.091</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C3">
-        <v>33267.112000000001</v>
+        <v>33943.661</v>
       </c>
       <c r="D3">
-        <v>31175.505000000001</v>
+        <v>31851.52</v>
       </c>
       <c r="E3">
-        <v>35346.167999999998</v>
+        <v>36024.168</v>
       </c>
       <c r="F3">
-        <v>327423.94099999999</v>
+        <v>335063.938</v>
       </c>
       <c r="G3">
-        <v>314910.033</v>
+        <v>322208.715</v>
       </c>
       <c r="H3">
-        <v>339916.53700000001</v>
+        <v>347901.662</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -589,39 +513,43 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>43542526515.595001</v>
+        <v>44561060370.542</v>
       </c>
       <c r="M3">
-        <v>41879092249.946999</v>
+        <v>42845684240.782</v>
       </c>
       <c r="N3">
-        <v>45221777852.945999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+        <v>46289903088.83</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C4">
-        <v>40418.99</v>
+        <v>38245.822</v>
       </c>
       <c r="D4">
-        <v>37938.565999999999</v>
+        <v>35874.844</v>
       </c>
       <c r="E4">
-        <v>42889.961000000003</v>
+        <v>40606.505</v>
       </c>
       <c r="F4">
-        <v>442385.07199999999</v>
+        <v>420670.744</v>
       </c>
       <c r="G4">
-        <v>426436.20600000001</v>
+        <v>405285.557</v>
       </c>
       <c r="H4">
-        <v>458349.74900000001</v>
+        <v>436057.938</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -633,567 +561,619 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>58846863486.456001</v>
+        <v>55958045376.332</v>
       </c>
       <c r="M4">
-        <v>56715847026.922997</v>
+        <v>53903811770.406</v>
       </c>
       <c r="N4">
-        <v>60986092072.639</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
+        <v>58018792859.753</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C5">
-        <v>23697.924999999999</v>
+        <v>22676.25</v>
       </c>
       <c r="D5">
-        <v>22335.302</v>
+        <v>21361.121</v>
       </c>
       <c r="E5">
-        <v>25071.975999999999</v>
+        <v>24007.82</v>
       </c>
       <c r="F5">
-        <v>19319.041000000001</v>
+        <v>30261.227</v>
       </c>
       <c r="G5">
-        <v>18308.508999999998</v>
+        <v>28632.05</v>
       </c>
       <c r="H5">
-        <v>20338.656999999999</v>
+        <v>31901.046</v>
       </c>
       <c r="I5">
-        <v>1320056785.6029999</v>
+        <v>1195190999.95</v>
       </c>
       <c r="J5">
-        <v>1243989370.4749999</v>
+        <v>1125755813.58</v>
       </c>
       <c r="K5">
-        <v>1396841057.494</v>
+        <v>1265295628.574</v>
       </c>
       <c r="L5">
-        <v>2569568285.112</v>
+        <v>4024844896.299</v>
       </c>
       <c r="M5">
-        <v>2435084861.4569998</v>
+        <v>3809200917.425</v>
       </c>
       <c r="N5">
-        <v>2704838419.6960001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
+        <v>4243204559.144</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C6">
-        <v>19304.705000000002</v>
+        <v>19817.172</v>
       </c>
       <c r="D6">
-        <v>18252.852999999999</v>
+        <v>18746.889</v>
       </c>
       <c r="E6">
-        <v>20371.583999999999</v>
+        <v>20907.059</v>
       </c>
       <c r="F6">
-        <v>16592.355</v>
+        <v>26651.353</v>
       </c>
       <c r="G6">
-        <v>15730.246999999999</v>
+        <v>25316.9</v>
       </c>
       <c r="H6">
-        <v>17473.909</v>
+        <v>28005.535</v>
       </c>
       <c r="I6">
-        <v>1075464482.1210001</v>
+        <v>1044444693.495</v>
       </c>
       <c r="J6">
-        <v>1016486063.516</v>
+        <v>987821981.398</v>
       </c>
       <c r="K6">
-        <v>1134949585.895</v>
+        <v>1101922530.912</v>
       </c>
       <c r="L6">
-        <v>2207280545.3850002</v>
+        <v>3545026854.35</v>
       </c>
       <c r="M6">
-        <v>2091761912.9349999</v>
+        <v>3367573570.482</v>
       </c>
       <c r="N6">
-        <v>2323870695.9109998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
+        <v>3724369063.177</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C7">
-        <v>27249.807000000001</v>
+        <v>24796.421</v>
       </c>
       <c r="D7">
-        <v>25872.542000000001</v>
+        <v>23504.828</v>
       </c>
       <c r="E7">
-        <v>28637.727999999999</v>
+        <v>26090.115</v>
       </c>
       <c r="F7">
-        <v>25227.159</v>
+        <v>34450.92</v>
       </c>
       <c r="G7">
-        <v>24091.991000000002</v>
+        <v>32810.891</v>
       </c>
       <c r="H7">
-        <v>26372.741999999998</v>
+        <v>36102.79</v>
       </c>
       <c r="I7">
-        <v>1518052981.053</v>
+        <v>1306741197.167</v>
       </c>
       <c r="J7">
-        <v>1440886429.8629999</v>
+        <v>1238605024.919</v>
       </c>
       <c r="K7">
-        <v>1595682985.2079999</v>
+        <v>1375173230.213</v>
       </c>
       <c r="L7">
-        <v>3355201911.441</v>
+        <v>4582021726.773</v>
       </c>
       <c r="M7">
-        <v>3204452471.7810001</v>
+        <v>4365018898.505</v>
       </c>
       <c r="N7">
-        <v>3507007826.428</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>4800439993.926</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C8">
-        <v>13887.759</v>
+        <v>4543.496</v>
       </c>
       <c r="D8">
-        <v>13084.311</v>
+        <v>4228.863</v>
       </c>
       <c r="E8">
-        <v>14712.902</v>
+        <v>4869.927</v>
       </c>
       <c r="F8">
-        <v>18478.91</v>
+        <v>2087.799</v>
       </c>
       <c r="G8">
-        <v>17118.839</v>
+        <v>1952.686</v>
       </c>
       <c r="H8">
-        <v>19945.991000000002</v>
+        <v>2227.967</v>
       </c>
       <c r="I8">
-        <v>205613521.80199999</v>
+        <v>133192201.793</v>
       </c>
       <c r="J8">
-        <v>193706414.51499999</v>
+        <v>123928300.469</v>
       </c>
       <c r="K8">
-        <v>217783810.914</v>
+        <v>142720561.019</v>
       </c>
       <c r="L8">
-        <v>2457606556.362</v>
+        <v>277648641.807</v>
       </c>
       <c r="M8">
-        <v>2276466284.2379999</v>
+        <v>259642221.488</v>
       </c>
       <c r="N8">
-        <v>2652927959.6680002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
+        <v>296263876.295</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C9">
-        <v>10935.385</v>
+        <v>3797.087</v>
       </c>
       <c r="D9">
-        <v>10307.172</v>
+        <v>3545.822</v>
       </c>
       <c r="E9">
-        <v>11582.142</v>
+        <v>4058.099</v>
       </c>
       <c r="F9">
-        <v>14801.262000000001</v>
+        <v>1749.931</v>
       </c>
       <c r="G9">
-        <v>13782.053</v>
+        <v>1641.338</v>
       </c>
       <c r="H9">
-        <v>15865.076999999999</v>
+        <v>1862.717</v>
       </c>
       <c r="I9">
-        <v>161916543.39500001</v>
+        <v>111303753.12</v>
       </c>
       <c r="J9">
-        <v>152619159.25299999</v>
+        <v>103967134.944</v>
       </c>
       <c r="K9">
-        <v>171561934.507</v>
+        <v>119030240.88</v>
       </c>
       <c r="L9">
-        <v>1968572551.6489999</v>
+        <v>232692414.02</v>
       </c>
       <c r="M9">
-        <v>1832807231.1129999</v>
+        <v>218241674.435</v>
       </c>
       <c r="N9">
-        <v>2111156946.8740001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
+        <v>247813562.631</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C10">
-        <v>20185.027999999998</v>
+        <v>5379.038</v>
       </c>
       <c r="D10">
-        <v>19168.591</v>
+        <v>5048.609</v>
       </c>
       <c r="E10">
-        <v>21219.991000000002</v>
+        <v>5721.084</v>
       </c>
       <c r="F10">
-        <v>31883.471000000001</v>
+        <v>2552.89</v>
       </c>
       <c r="G10">
-        <v>29961.68</v>
+        <v>2403.875</v>
       </c>
       <c r="H10">
-        <v>33863.237999999998</v>
+        <v>2705.427</v>
       </c>
       <c r="I10">
-        <v>298859017.29799998</v>
+        <v>157721100.077</v>
       </c>
       <c r="J10">
-        <v>283878779.463</v>
+        <v>148037237.686</v>
       </c>
       <c r="K10">
-        <v>314277325.03200001</v>
+        <v>167787435.507</v>
       </c>
       <c r="L10">
-        <v>4240090894.026</v>
+        <v>339488086.163</v>
       </c>
       <c r="M10">
-        <v>3986080225.4749999</v>
+        <v>319748790.824</v>
       </c>
       <c r="N10">
-        <v>4502223239.2449999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
+        <v>359708837.949</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C11">
-        <v>2942.3939999999998</v>
+        <v>2728.93</v>
       </c>
       <c r="D11">
-        <v>2772.886</v>
+        <v>2571.544</v>
       </c>
       <c r="E11">
-        <v>3115.4459999999999</v>
+        <v>2890.135</v>
       </c>
       <c r="F11">
-        <v>5216.5069999999996</v>
+        <v>5473.89</v>
       </c>
       <c r="G11">
-        <v>4905.4489999999996</v>
+        <v>5132.651</v>
       </c>
       <c r="H11">
-        <v>5537.4449999999997</v>
+        <v>5833.075</v>
       </c>
       <c r="I11">
-        <v>221279871.736</v>
+        <v>106976591.662</v>
       </c>
       <c r="J11">
-        <v>208504949.59599999</v>
+        <v>100805170.227</v>
       </c>
       <c r="K11">
-        <v>234311993.74599999</v>
+        <v>113309787.295</v>
       </c>
       <c r="L11">
-        <v>693825457.704</v>
+        <v>728077425.442</v>
       </c>
       <c r="M11">
-        <v>652445074.47000003</v>
+        <v>682390843.98</v>
       </c>
       <c r="N11">
-        <v>736366505.05499995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
+        <v>775616687.804</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C12">
-        <v>2409.239</v>
+        <v>2422.289</v>
       </c>
       <c r="D12">
-        <v>2265.6959999999999</v>
+        <v>2278.441</v>
       </c>
       <c r="E12">
-        <v>2554.297</v>
+        <v>2570.257</v>
       </c>
       <c r="F12">
-        <v>4366.8959999999997</v>
+        <v>4666.588</v>
       </c>
       <c r="G12">
-        <v>4099.4840000000004</v>
+        <v>4382.483</v>
       </c>
       <c r="H12">
-        <v>4643.1980000000003</v>
+        <v>4961.542</v>
       </c>
       <c r="I12">
-        <v>181173287.97099999</v>
+        <v>94963457.906</v>
       </c>
       <c r="J12">
-        <v>170473800.35299999</v>
+        <v>89331748.27599999</v>
       </c>
       <c r="K12">
-        <v>192187854.86199999</v>
+        <v>100761140.409</v>
       </c>
       <c r="L12">
-        <v>580768844.84099996</v>
+        <v>620610376.397</v>
       </c>
       <c r="M12">
-        <v>545160638.20200002</v>
+        <v>582974961.24</v>
       </c>
       <c r="N12">
-        <v>617299114.92900002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
+        <v>659839757.794</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C13">
-        <v>4401.2809999999999</v>
+        <v>4028.539</v>
       </c>
       <c r="D13">
-        <v>4184.4309999999996</v>
+        <v>3820.021</v>
       </c>
       <c r="E13">
-        <v>4621.53</v>
+        <v>4241.037</v>
       </c>
       <c r="F13">
-        <v>9029.0169999999998</v>
+        <v>6952.788</v>
       </c>
       <c r="G13">
-        <v>8567.4629999999997</v>
+        <v>6573.004</v>
       </c>
       <c r="H13">
-        <v>9503.6740000000009</v>
+        <v>7348.083</v>
       </c>
       <c r="I13">
-        <v>331014953.61400002</v>
+        <v>157919933.87</v>
       </c>
       <c r="J13">
-        <v>314799737.97600001</v>
+        <v>149763818.921</v>
       </c>
       <c r="K13">
-        <v>347564497.68900001</v>
+        <v>166243999.281</v>
       </c>
       <c r="L13">
-        <v>1200787486.6589999</v>
+        <v>924736045.862</v>
       </c>
       <c r="M13">
-        <v>1139180263.4000001</v>
+        <v>873805309.196</v>
       </c>
       <c r="N13">
-        <v>1263827709.2839999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
+        <v>977057159.401</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C14">
-        <v>8354.17</v>
+        <v>7964.811</v>
       </c>
       <c r="D14">
-        <v>7716.5609999999997</v>
+        <v>7364.337</v>
       </c>
       <c r="E14">
-        <v>8998.4459999999999</v>
+        <v>8572.624</v>
       </c>
       <c r="F14">
-        <v>12955.635</v>
+        <v>9082.628000000001</v>
       </c>
       <c r="G14">
-        <v>12111.835999999999</v>
+        <v>8384.610000000001</v>
       </c>
       <c r="H14">
-        <v>13811.007</v>
+        <v>9789.531999999999</v>
       </c>
       <c r="I14">
-        <v>140693170.13600001</v>
+        <v>132612389.522</v>
       </c>
       <c r="J14">
-        <v>129996219.53300001</v>
+        <v>122631310.954</v>
       </c>
       <c r="K14">
-        <v>151534077.24700001</v>
+        <v>142713020.186</v>
       </c>
       <c r="L14">
-        <v>1722819519.5079999</v>
+        <v>1207868691.837</v>
       </c>
       <c r="M14">
-        <v>1610248463.8380001</v>
+        <v>1114855115.658</v>
       </c>
       <c r="N14">
-        <v>1836779203.1919999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
+        <v>1302097491.55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C15">
-        <v>6510.3410000000003</v>
+        <v>6622.005</v>
       </c>
       <c r="D15">
-        <v>6006.1869999999999</v>
+        <v>6127.231</v>
       </c>
       <c r="E15">
-        <v>7023.7460000000001</v>
+        <v>7127.814</v>
       </c>
       <c r="F15">
-        <v>10360.11</v>
+        <v>7543.314</v>
       </c>
       <c r="G15">
-        <v>9744.4279999999999</v>
+        <v>6963.935</v>
       </c>
       <c r="H15">
-        <v>10984.788</v>
+        <v>8136.022</v>
       </c>
       <c r="I15">
-        <v>109611923.764</v>
+        <v>110230198.529</v>
       </c>
       <c r="J15">
-        <v>101107908.882</v>
+        <v>101951060.666</v>
       </c>
       <c r="K15">
-        <v>118225431.994</v>
+        <v>118624443.985</v>
       </c>
       <c r="L15">
-        <v>1377714036.1789999</v>
+        <v>1003178089.908</v>
       </c>
       <c r="M15">
-        <v>1296088461.5220001</v>
+        <v>926044819.365</v>
       </c>
       <c r="N15">
-        <v>1461357977.197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
+        <v>1082515638.592</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C16">
-        <v>9256.9930000000004</v>
+        <v>8396.795</v>
       </c>
       <c r="D16">
-        <v>8593.7240000000002</v>
+        <v>7775.929</v>
       </c>
       <c r="E16">
-        <v>9926.4670000000006</v>
+        <v>9023.387000000001</v>
       </c>
       <c r="F16">
-        <v>15637.982</v>
+        <v>9595.795</v>
       </c>
       <c r="G16">
-        <v>14726.846</v>
+        <v>8870.436</v>
       </c>
       <c r="H16">
-        <v>16566.756000000001</v>
+        <v>10332.776</v>
       </c>
       <c r="I16">
-        <v>155894440.92199999</v>
+        <v>139812873.545</v>
       </c>
       <c r="J16">
-        <v>144717717.16</v>
+        <v>129458099.404</v>
       </c>
       <c r="K16">
-        <v>167165893.565</v>
+        <v>150321778.47</v>
       </c>
       <c r="L16">
-        <v>2080265419.7130001</v>
+        <v>1276285006.434</v>
       </c>
       <c r="M16">
-        <v>1958708067.075</v>
+        <v>1180085815.914</v>
       </c>
       <c r="N16">
-        <v>2203165117.3909998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
+        <v>1374305021.307</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C17">
-        <v>60829.48</v>
+        <v>55990.867</v>
       </c>
       <c r="D17">
-        <v>57592.822999999997</v>
+        <v>53171.19</v>
       </c>
       <c r="E17">
-        <v>64109.597999999998</v>
+        <v>58829.584</v>
       </c>
       <c r="F17">
-        <v>17561.321</v>
+        <v>18470.001</v>
       </c>
       <c r="G17">
-        <v>16188.766</v>
+        <v>17212.792</v>
       </c>
       <c r="H17">
-        <v>19003.63</v>
+        <v>19744.413</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1205,39 +1185,43 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>2335879013.665</v>
+        <v>2456836665.638</v>
       </c>
       <c r="M17">
-        <v>2152736590.901</v>
+        <v>2288770300.347</v>
       </c>
       <c r="N17">
-        <v>2526434424.605</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
+        <v>2626444184.343</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C18">
-        <v>47885.324999999997</v>
+        <v>47378.248</v>
       </c>
       <c r="D18">
-        <v>45511.245999999999</v>
+        <v>45104.185</v>
       </c>
       <c r="E18">
-        <v>50247.678999999996</v>
+        <v>49640.39</v>
       </c>
       <c r="F18">
-        <v>13920.004999999999</v>
+        <v>15828.167</v>
       </c>
       <c r="G18">
-        <v>13006.974</v>
+        <v>14848.809</v>
       </c>
       <c r="H18">
-        <v>14850.111000000001</v>
+        <v>16807.678</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1249,39 +1233,43 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1851655339.4000001</v>
+        <v>2105432826.388</v>
       </c>
       <c r="M18">
-        <v>1730690397.0580001</v>
+        <v>1975755839.026</v>
       </c>
       <c r="N18">
-        <v>1975411886.632</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
+        <v>2235837863.468</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C19">
-        <v>100888.15399999999</v>
+        <v>91940.137</v>
       </c>
       <c r="D19">
-        <v>96595.337</v>
+        <v>87865.107</v>
       </c>
       <c r="E19">
-        <v>105195.71</v>
+        <v>96036.04700000001</v>
       </c>
       <c r="F19">
-        <v>34094.347000000002</v>
+        <v>36427.248</v>
       </c>
       <c r="G19">
-        <v>32173.223999999998</v>
+        <v>34362.541</v>
       </c>
       <c r="H19">
-        <v>36053.266000000003</v>
+        <v>38500.733</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1293,171 +1281,187 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>4535167093.5050001</v>
+        <v>4844719266.443</v>
       </c>
       <c r="M19">
-        <v>4281631303.2080002</v>
+        <v>4572938335.861</v>
       </c>
       <c r="N19">
-        <v>4794812563.599</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
+        <v>5120144777.643</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C20">
-        <v>45008.171999999999</v>
+        <v>13719.621</v>
       </c>
       <c r="D20">
-        <v>42560.074000000001</v>
+        <v>12823.294</v>
       </c>
       <c r="E20">
-        <v>47515.035000000003</v>
+        <v>14649.11</v>
       </c>
       <c r="F20">
-        <v>65163.642999999996</v>
+        <v>6390.62</v>
       </c>
       <c r="G20">
-        <v>60862.572</v>
+        <v>5997.898999999999</v>
       </c>
       <c r="H20">
-        <v>69674.305999999997</v>
+        <v>6796.111000000001</v>
       </c>
       <c r="I20">
-        <v>666389082.495</v>
+        <v>402217054.99</v>
       </c>
       <c r="J20">
-        <v>630204353.23099995</v>
+        <v>375932673.099</v>
       </c>
       <c r="K20">
-        <v>703623070.45300007</v>
+        <v>429538237.406</v>
       </c>
       <c r="L20">
-        <v>8666270002.0369987</v>
+        <v>849829141.99</v>
       </c>
       <c r="M20">
-        <v>8095353740.8260002</v>
+        <v>797632686.747</v>
       </c>
       <c r="N20">
-        <v>9266308145.7869987</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
+        <v>903786276.875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C21">
-        <v>70252.437000000005</v>
+        <v>67289.84299999999</v>
       </c>
       <c r="D21">
-        <v>66460.697</v>
+        <v>63612.838</v>
       </c>
       <c r="E21">
-        <v>74081.288</v>
+        <v>71004.99400000001</v>
       </c>
       <c r="F21">
-        <v>61138.555</v>
+        <v>91363.5</v>
       </c>
       <c r="G21">
-        <v>58130.747000000003</v>
+        <v>86759.841</v>
       </c>
       <c r="H21">
-        <v>64185.307999999997</v>
+        <v>96009.371</v>
       </c>
       <c r="I21">
-        <v>3913574248.777</v>
+        <v>3546376890.612</v>
       </c>
       <c r="J21">
-        <v>3701361863.8540001</v>
+        <v>3352182819.897</v>
       </c>
       <c r="K21">
-        <v>4127473628.5970001</v>
+        <v>3742391389.699</v>
       </c>
       <c r="L21">
-        <v>8132050741.9379997</v>
+        <v>12151893477.422</v>
       </c>
       <c r="M21">
-        <v>7731299246.1730003</v>
+        <v>11541793386.412</v>
       </c>
       <c r="N21">
-        <v>8535716942.0349998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
+        <v>12768013616.247</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C22">
-        <v>24121.504000000001</v>
+        <v>22983.611</v>
       </c>
       <c r="D22">
-        <v>22316.472000000002</v>
+        <v>21267.497</v>
       </c>
       <c r="E22">
-        <v>25948.659</v>
+        <v>24723.825</v>
       </c>
       <c r="F22">
-        <v>38953.726999999999</v>
+        <v>26221.737</v>
       </c>
       <c r="G22">
-        <v>36583.11</v>
+        <v>24218.981</v>
       </c>
       <c r="H22">
-        <v>41362.550999999999</v>
+        <v>28258.33</v>
       </c>
       <c r="I22">
-        <v>406199534.82200003</v>
+        <v>382655461.596</v>
       </c>
       <c r="J22">
-        <v>375821845.57499999</v>
+        <v>354040471.024</v>
       </c>
       <c r="K22">
-        <v>436925402.80599999</v>
+        <v>411659242.641</v>
       </c>
       <c r="L22">
-        <v>5180798975.3999996</v>
+        <v>3487331788.179</v>
       </c>
       <c r="M22">
-        <v>4865044992.4350004</v>
+        <v>3220985750.937</v>
       </c>
       <c r="N22">
-        <v>5501302297.7799997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
+        <v>3758918151.449</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C23">
-        <v>209602.959</v>
+        <v>195309.252</v>
       </c>
       <c r="D23">
-        <v>199699.40599999999</v>
+        <v>186140.482</v>
       </c>
       <c r="E23">
-        <v>219552.98699999999</v>
+        <v>204506.021</v>
       </c>
       <c r="F23">
-        <v>65575.67300000001</v>
+        <v>70725.416</v>
       </c>
       <c r="G23">
-        <v>61368.963999999993</v>
+        <v>66424.14199999999</v>
       </c>
       <c r="H23">
-        <v>69907.007000000012</v>
+        <v>75052.82399999999</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1469,83 +1473,91 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>8722701446.5699997</v>
+        <v>9406988758.469</v>
       </c>
       <c r="M23">
-        <v>8165058291.1669998</v>
+        <v>8837464475.234001</v>
       </c>
       <c r="N23">
-        <v>9296658874.8359985</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
+        <v>9982426825.453999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C24">
-        <v>9752.9140000000007</v>
+        <v>9179.758</v>
       </c>
       <c r="D24">
-        <v>9223.012999999999</v>
+        <v>8670.005999999999</v>
       </c>
       <c r="E24">
-        <v>10291.272999999999</v>
+        <v>9701.429</v>
       </c>
       <c r="F24">
-        <v>18612.419999999998</v>
+        <v>17093.266</v>
       </c>
       <c r="G24">
-        <v>17572.396000000001</v>
+        <v>16088.138</v>
       </c>
       <c r="H24">
-        <v>19684.316999999999</v>
+        <v>18142.7</v>
       </c>
       <c r="I24">
-        <v>733468113.3210001</v>
+        <v>359859983.438</v>
       </c>
       <c r="J24">
-        <v>693778487.92499995</v>
+        <v>339900737.424</v>
       </c>
       <c r="K24">
-        <v>774064346.29699993</v>
+        <v>380314926.985</v>
       </c>
       <c r="L24">
-        <v>2475381789.204</v>
+        <v>2273423847.701</v>
       </c>
       <c r="M24">
-        <v>2336785976.072</v>
+        <v>2139171114.416</v>
       </c>
       <c r="N24">
-        <v>2617493329.2680001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
+        <v>2412513604.999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C25">
-        <v>110492.41</v>
+        <v>107934.032</v>
       </c>
       <c r="D25">
-        <v>103334.398</v>
+        <v>100964.534</v>
       </c>
       <c r="E25">
-        <v>117630.289</v>
+        <v>114878.933</v>
       </c>
       <c r="F25">
-        <v>1111325.8359999999</v>
+        <v>1087079.874</v>
       </c>
       <c r="G25">
-        <v>1068286.2490000001</v>
+        <v>1044616.865</v>
       </c>
       <c r="H25">
-        <v>1154364.4879999999</v>
+        <v>1129563.021</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1557,233 +1569,253 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>147811881791.09</v>
+        <v>144588786837.826</v>
       </c>
       <c r="M25">
-        <v>142075826019.59299</v>
+        <v>138918235953.446</v>
       </c>
       <c r="N25">
-        <v>153573264702.60999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
+        <v>150273400287.674</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C26">
-        <v>146518.03599999999</v>
+        <v>129648.903</v>
       </c>
       <c r="D26">
-        <v>137722.21</v>
+        <v>121935.225</v>
       </c>
       <c r="E26">
-        <v>155402.52799999999</v>
+        <v>137418.35</v>
       </c>
       <c r="F26">
-        <v>415048.23700000002</v>
+        <v>396720.737</v>
       </c>
       <c r="G26">
-        <v>395573.40899999999</v>
+        <v>378437.382</v>
       </c>
       <c r="H26">
-        <v>434734.93199999997</v>
+        <v>415099.454</v>
       </c>
       <c r="I26">
-        <v>1887643349.277</v>
+        <v>1567972182.927</v>
       </c>
       <c r="J26">
-        <v>1776196954.119</v>
+        <v>1473120595.23</v>
       </c>
       <c r="K26">
-        <v>2000470939.401</v>
+        <v>1664038997.074</v>
       </c>
       <c r="L26">
-        <v>55202190621.390007</v>
+        <v>52764957411.97501</v>
       </c>
       <c r="M26">
-        <v>52607868017.626999</v>
+        <v>50323599341.15601</v>
       </c>
       <c r="N26">
-        <v>57822741289.240997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
+        <v>55208331138.22701</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C27">
-        <v>120312.107</v>
+        <v>113980.462</v>
       </c>
       <c r="D27">
-        <v>113518.659</v>
+        <v>107654.088</v>
       </c>
       <c r="E27">
-        <v>127125.61599999999</v>
+        <v>120327.787</v>
       </c>
       <c r="F27">
-        <v>387464.56900000002</v>
+        <v>391503.291</v>
       </c>
       <c r="G27">
-        <v>371273.21899999998</v>
+        <v>375362.1800000001</v>
       </c>
       <c r="H27">
-        <v>403733.61999999988</v>
+        <v>407675.156</v>
       </c>
       <c r="I27">
-        <v>1528166237.2509999</v>
+        <v>1360942103.05</v>
       </c>
       <c r="J27">
-        <v>1440686932.0039999</v>
+        <v>1283071925.284</v>
       </c>
       <c r="K27">
-        <v>1616924807.2579999</v>
+        <v>1440338356.186</v>
       </c>
       <c r="L27">
-        <v>51528517833.049011</v>
+        <v>52068000931.605</v>
       </c>
       <c r="M27">
-        <v>49375600890.777</v>
+        <v>49916275105.32999</v>
       </c>
       <c r="N27">
-        <v>53710874474.488998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
+        <v>54240278974.492</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C28">
-        <v>202400.253</v>
+        <v>172786.752</v>
       </c>
       <c r="D28">
-        <v>192353.19099999999</v>
+        <v>163889.338</v>
       </c>
       <c r="E28">
-        <v>212491.38699999999</v>
+        <v>181718.175</v>
       </c>
       <c r="F28">
-        <v>558257.04799999995</v>
+        <v>510650.385</v>
       </c>
       <c r="G28">
-        <v>535957.41</v>
+        <v>490306.304</v>
       </c>
       <c r="H28">
-        <v>580709.42500000005</v>
+        <v>531047.747</v>
       </c>
       <c r="I28">
-        <v>2303821392.8870001</v>
+        <v>1762195104.659</v>
       </c>
       <c r="J28">
-        <v>2184282664.4619999</v>
+        <v>1665864180.93</v>
       </c>
       <c r="K28">
-        <v>2424690701.494</v>
+        <v>1859526443.471</v>
       </c>
       <c r="L28">
-        <v>74258376291.800003</v>
+        <v>67925295508.007</v>
       </c>
       <c r="M28">
-        <v>71285899357.862</v>
+        <v>65215408920.70599</v>
       </c>
       <c r="N28">
-        <v>77257128528.585999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
+        <v>70650448649.979</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C29">
-        <v>469230.39599999989</v>
+        <v>416416.117</v>
       </c>
       <c r="D29">
-        <v>443594.05999999988</v>
+        <v>393478.651</v>
       </c>
       <c r="E29">
-        <v>495019.53100000002</v>
+        <v>439464.312</v>
       </c>
       <c r="F29">
-        <v>1360769.8540000001</v>
+        <v>1298874.412999999</v>
       </c>
       <c r="G29">
-        <v>1302804.0379999999</v>
+        <v>1244105.866</v>
       </c>
       <c r="H29">
-        <v>1419177.977</v>
+        <v>1353822.357</v>
       </c>
       <c r="I29">
-        <v>5719630979.415</v>
+        <v>4691109390.636002</v>
       </c>
       <c r="J29">
-        <v>5401166550.5849991</v>
+        <v>4422056701.443999</v>
       </c>
       <c r="K29">
-        <v>6042086448.1529989</v>
+        <v>4963903796.731001</v>
       </c>
       <c r="L29">
-        <v>180989084746.23901</v>
+        <v>172758253851.587</v>
       </c>
       <c r="M29">
-        <v>173269368266.26611</v>
+        <v>165455283367.192</v>
       </c>
       <c r="N29">
-        <v>188790744292.31601</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
+        <v>180099058762.698</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chronic diseases</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C30">
-        <v>358737.98599999998</v>
+        <v>194494.742</v>
       </c>
       <c r="D30">
-        <v>340259.66200000001</v>
+        <v>183329.34</v>
       </c>
       <c r="E30">
-        <v>377389.24200000003</v>
+        <v>205743.916</v>
       </c>
       <c r="F30">
-        <v>249444.01800000001</v>
+        <v>491961.2280000001</v>
       </c>
       <c r="G30">
-        <v>234517.78899999999</v>
+        <v>470122.383</v>
       </c>
       <c r="H30">
-        <v>264813.48900000012</v>
+        <v>513915.852</v>
       </c>
       <c r="I30">
-        <v>5719630979.415</v>
+        <v>4691109390.636002</v>
       </c>
       <c r="J30">
-        <v>5401166550.5849991</v>
+        <v>4422056701.443999</v>
       </c>
       <c r="K30">
-        <v>6042086448.1529989</v>
+        <v>4963903796.731001</v>
       </c>
       <c r="L30">
-        <v>33177202955.148998</v>
+        <v>65428971452.222</v>
       </c>
       <c r="M30">
-        <v>31193542246.673</v>
+        <v>62521023018.31999</v>
       </c>
       <c r="N30">
-        <v>35217479589.706001</v>
+        <v>68368972601.868</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -1782,22 +1782,22 @@
         </is>
       </c>
       <c r="C30">
-        <v>194494.742</v>
+        <v>113172.833</v>
       </c>
       <c r="D30">
-        <v>183329.34</v>
+        <v>106373.635</v>
       </c>
       <c r="E30">
-        <v>205743.916</v>
+        <v>120079.358</v>
       </c>
       <c r="F30">
-        <v>491961.2280000001</v>
+        <v>141069.123</v>
       </c>
       <c r="G30">
-        <v>470122.383</v>
+        <v>133064.859</v>
       </c>
       <c r="H30">
-        <v>513915.852</v>
+        <v>149206.512</v>
       </c>
       <c r="I30">
         <v>4691109390.636002</v>
@@ -1809,13 +1809,13 @@
         <v>4963903796.731001</v>
       </c>
       <c r="L30">
-        <v>65428971452.222</v>
+        <v>18762478255.292</v>
       </c>
       <c r="M30">
-        <v>62521023018.31999</v>
+        <v>17699582938.512</v>
       </c>
       <c r="N30">
-        <v>68368972601.868</v>
+        <v>19843231649.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -1,21 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314D34DA-8DBA-2845-A889-484ECBBD8390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>periurban</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Chronic diseases</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +162,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +214,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +248,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +283,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,95 +459,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>35744.549</v>
+        <v>35744.548999999999</v>
       </c>
       <c r="D2">
         <v>33238.17</v>
@@ -447,13 +524,13 @@
         <v>38248.26</v>
       </c>
       <c r="F2">
-        <v>331345.192</v>
+        <v>331345.19199999998</v>
       </c>
       <c r="G2">
-        <v>317122.593</v>
+        <v>317122.59299999999</v>
       </c>
       <c r="H2">
-        <v>345603.421</v>
+        <v>345603.42099999997</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,25 +542,21 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>44069681090.952</v>
+        <v>44069681090.952003</v>
       </c>
       <c r="M2">
-        <v>42168739942.258</v>
+        <v>42168739942.258003</v>
       </c>
       <c r="N2">
-        <v>45964704339.091</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>45964704339.091003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
         <v>33943.661</v>
@@ -492,16 +565,16 @@
         <v>31851.52</v>
       </c>
       <c r="E3">
-        <v>36024.168</v>
+        <v>36024.167999999998</v>
       </c>
       <c r="F3">
-        <v>335063.938</v>
+        <v>335063.93800000002</v>
       </c>
       <c r="G3">
-        <v>322208.715</v>
+        <v>322208.71500000003</v>
       </c>
       <c r="H3">
-        <v>347901.662</v>
+        <v>347901.66200000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -516,40 +589,36 @@
         <v>44561060370.542</v>
       </c>
       <c r="M3">
-        <v>42845684240.782</v>
+        <v>42845684240.781998</v>
       </c>
       <c r="N3">
-        <v>46289903088.83</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>46289903088.830002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>38245.822</v>
       </c>
       <c r="D4">
-        <v>35874.844</v>
+        <v>35874.843999999997</v>
       </c>
       <c r="E4">
-        <v>40606.505</v>
+        <v>40606.504999999997</v>
       </c>
       <c r="F4">
-        <v>420670.744</v>
+        <v>420670.74400000001</v>
       </c>
       <c r="G4">
-        <v>405285.557</v>
+        <v>405285.55699999997</v>
       </c>
       <c r="H4">
-        <v>436057.938</v>
+        <v>436057.93800000002</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,85 +630,77 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>55958045376.332</v>
+        <v>55958045376.332001</v>
       </c>
       <c r="M4">
-        <v>53903811770.406</v>
+        <v>53903811770.405998</v>
       </c>
       <c r="N4">
-        <v>58018792859.753</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>58018792859.752998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
         <v>22676.25</v>
       </c>
       <c r="D5">
-        <v>21361.121</v>
+        <v>21361.120999999999</v>
       </c>
       <c r="E5">
         <v>24007.82</v>
       </c>
       <c r="F5">
-        <v>30261.227</v>
+        <v>30261.226999999999</v>
       </c>
       <c r="G5">
         <v>28632.05</v>
       </c>
       <c r="H5">
-        <v>31901.046</v>
+        <v>31901.045999999998</v>
       </c>
       <c r="I5">
         <v>1195190999.95</v>
       </c>
       <c r="J5">
-        <v>1125755813.58</v>
+        <v>1125755813.5799999</v>
       </c>
       <c r="K5">
-        <v>1265295628.574</v>
+        <v>1265295628.5739999</v>
       </c>
       <c r="L5">
-        <v>4024844896.299</v>
+        <v>4024844896.2989998</v>
       </c>
       <c r="M5">
-        <v>3809200917.425</v>
+        <v>3809200917.4250002</v>
       </c>
       <c r="N5">
-        <v>4243204559.144</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>4243204559.1440001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>19817.172</v>
+        <v>19817.171999999999</v>
       </c>
       <c r="D6">
-        <v>18746.889</v>
+        <v>18746.888999999999</v>
       </c>
       <c r="E6">
-        <v>20907.059</v>
+        <v>20907.059000000001</v>
       </c>
       <c r="F6">
-        <v>26651.353</v>
+        <v>26651.352999999999</v>
       </c>
       <c r="G6">
         <v>25316.9</v>
@@ -654,94 +715,86 @@
         <v>987821981.398</v>
       </c>
       <c r="K6">
-        <v>1101922530.912</v>
+        <v>1101922530.9119999</v>
       </c>
       <c r="L6">
-        <v>3545026854.35</v>
+        <v>3545026854.3499999</v>
       </c>
       <c r="M6">
-        <v>3367573570.482</v>
+        <v>3367573570.4819999</v>
       </c>
       <c r="N6">
         <v>3724369063.177</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>24796.421</v>
+        <v>24796.420999999998</v>
       </c>
       <c r="D7">
-        <v>23504.828</v>
+        <v>23504.828000000001</v>
       </c>
       <c r="E7">
-        <v>26090.115</v>
+        <v>26090.115000000002</v>
       </c>
       <c r="F7">
         <v>34450.92</v>
       </c>
       <c r="G7">
-        <v>32810.891</v>
+        <v>32810.891000000003</v>
       </c>
       <c r="H7">
         <v>36102.79</v>
       </c>
       <c r="I7">
-        <v>1306741197.167</v>
+        <v>1306741197.1670001</v>
       </c>
       <c r="J7">
-        <v>1238605024.919</v>
+        <v>1238605024.9189999</v>
       </c>
       <c r="K7">
-        <v>1375173230.213</v>
+        <v>1375173230.2130001</v>
       </c>
       <c r="L7">
-        <v>4582021726.773</v>
+        <v>4582021726.7729998</v>
       </c>
       <c r="M7">
-        <v>4365018898.505</v>
+        <v>4365018898.5050001</v>
       </c>
       <c r="N7">
-        <v>4800439993.926</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>4800439993.9259996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>4543.496</v>
+        <v>4543.4960000000001</v>
       </c>
       <c r="D8">
-        <v>4228.863</v>
+        <v>4228.8630000000003</v>
       </c>
       <c r="E8">
-        <v>4869.927</v>
+        <v>4869.9269999999997</v>
       </c>
       <c r="F8">
         <v>2087.799</v>
       </c>
       <c r="G8">
-        <v>1952.686</v>
+        <v>1952.6859999999999</v>
       </c>
       <c r="H8">
-        <v>2227.967</v>
+        <v>2227.9670000000001</v>
       </c>
       <c r="I8">
         <v>133192201.793</v>
@@ -750,37 +803,33 @@
         <v>123928300.469</v>
       </c>
       <c r="K8">
-        <v>142720561.019</v>
+        <v>142720561.01899999</v>
       </c>
       <c r="L8">
-        <v>277648641.807</v>
+        <v>277648641.80699998</v>
       </c>
       <c r="M8">
-        <v>259642221.488</v>
+        <v>259642221.48800001</v>
       </c>
       <c r="N8">
-        <v>296263876.295</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>296263876.29500002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
         <v>3797.087</v>
       </c>
       <c r="D9">
-        <v>3545.822</v>
+        <v>3545.8220000000001</v>
       </c>
       <c r="E9">
-        <v>4058.099</v>
+        <v>4058.0990000000002</v>
       </c>
       <c r="F9">
         <v>1749.931</v>
@@ -789,46 +838,42 @@
         <v>1641.338</v>
       </c>
       <c r="H9">
-        <v>1862.717</v>
+        <v>1862.7170000000001</v>
       </c>
       <c r="I9">
         <v>111303753.12</v>
       </c>
       <c r="J9">
-        <v>103967134.944</v>
+        <v>103967134.94400001</v>
       </c>
       <c r="K9">
         <v>119030240.88</v>
       </c>
       <c r="L9">
-        <v>232692414.02</v>
+        <v>232692414.02000001</v>
       </c>
       <c r="M9">
         <v>218241674.435</v>
       </c>
       <c r="N9">
-        <v>247813562.631</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>247813562.63100001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>5379.038</v>
+        <v>5379.0379999999996</v>
       </c>
       <c r="D10">
-        <v>5048.609</v>
+        <v>5048.6090000000004</v>
       </c>
       <c r="E10">
-        <v>5721.084</v>
+        <v>5721.0839999999998</v>
       </c>
       <c r="F10">
         <v>2552.89</v>
@@ -837,19 +882,19 @@
         <v>2403.875</v>
       </c>
       <c r="H10">
-        <v>2705.427</v>
+        <v>2705.4270000000001</v>
       </c>
       <c r="I10">
-        <v>157721100.077</v>
+        <v>157721100.07699999</v>
       </c>
       <c r="J10">
-        <v>148037237.686</v>
+        <v>148037237.68599999</v>
       </c>
       <c r="K10">
         <v>167787435.507</v>
       </c>
       <c r="L10">
-        <v>339488086.163</v>
+        <v>339488086.16299999</v>
       </c>
       <c r="M10">
         <v>319748790.824</v>
@@ -858,34 +903,30 @@
         <v>359708837.949</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
         <v>2728.93</v>
       </c>
       <c r="D11">
-        <v>2571.544</v>
+        <v>2571.5439999999999</v>
       </c>
       <c r="E11">
-        <v>2890.135</v>
+        <v>2890.1350000000002</v>
       </c>
       <c r="F11">
         <v>5473.89</v>
       </c>
       <c r="G11">
-        <v>5132.651</v>
+        <v>5132.6509999999998</v>
       </c>
       <c r="H11">
-        <v>5833.075</v>
+        <v>5833.0749999999998</v>
       </c>
       <c r="I11">
         <v>106976591.662</v>
@@ -897,91 +938,83 @@
         <v>113309787.295</v>
       </c>
       <c r="L11">
-        <v>728077425.442</v>
+        <v>728077425.44200003</v>
       </c>
       <c r="M11">
-        <v>682390843.98</v>
+        <v>682390843.98000002</v>
       </c>
       <c r="N11">
-        <v>775616687.804</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>775616687.80400002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>2422.289</v>
+        <v>2422.2890000000002</v>
       </c>
       <c r="D12">
-        <v>2278.441</v>
+        <v>2278.4409999999998</v>
       </c>
       <c r="E12">
-        <v>2570.257</v>
+        <v>2570.2570000000001</v>
       </c>
       <c r="F12">
-        <v>4666.588</v>
+        <v>4666.5879999999997</v>
       </c>
       <c r="G12">
-        <v>4382.483</v>
+        <v>4382.4830000000002</v>
       </c>
       <c r="H12">
-        <v>4961.542</v>
+        <v>4961.5420000000004</v>
       </c>
       <c r="I12">
-        <v>94963457.906</v>
+        <v>94963457.906000003</v>
       </c>
       <c r="J12">
-        <v>89331748.27599999</v>
+        <v>89331748.275999993</v>
       </c>
       <c r="K12">
-        <v>100761140.409</v>
+        <v>100761140.40899999</v>
       </c>
       <c r="L12">
-        <v>620610376.397</v>
+        <v>620610376.39699996</v>
       </c>
       <c r="M12">
-        <v>582974961.24</v>
+        <v>582974961.24000001</v>
       </c>
       <c r="N12">
-        <v>659839757.794</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>659839757.79400003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>4028.539</v>
+        <v>4028.5390000000002</v>
       </c>
       <c r="D13">
-        <v>3820.021</v>
+        <v>3820.0210000000002</v>
       </c>
       <c r="E13">
-        <v>4241.037</v>
+        <v>4241.0370000000003</v>
       </c>
       <c r="F13">
-        <v>6952.788</v>
+        <v>6952.7879999999996</v>
       </c>
       <c r="G13">
-        <v>6573.004</v>
+        <v>6573.0039999999999</v>
       </c>
       <c r="H13">
-        <v>7348.083</v>
+        <v>7348.0829999999996</v>
       </c>
       <c r="I13">
         <v>157919933.87</v>
@@ -990,46 +1023,42 @@
         <v>149763818.921</v>
       </c>
       <c r="K13">
-        <v>166243999.281</v>
+        <v>166243999.28099999</v>
       </c>
       <c r="L13">
-        <v>924736045.862</v>
+        <v>924736045.86199999</v>
       </c>
       <c r="M13">
-        <v>873805309.196</v>
+        <v>873805309.19599998</v>
       </c>
       <c r="N13">
-        <v>977057159.401</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>977057159.40100002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>7964.811</v>
+        <v>7964.8109999999997</v>
       </c>
       <c r="D14">
-        <v>7364.337</v>
+        <v>7364.3370000000004</v>
       </c>
       <c r="E14">
-        <v>8572.624</v>
+        <v>8572.6239999999998</v>
       </c>
       <c r="F14">
-        <v>9082.628000000001</v>
+        <v>9082.6280000000006</v>
       </c>
       <c r="G14">
-        <v>8384.610000000001</v>
+        <v>8384.61</v>
       </c>
       <c r="H14">
-        <v>9789.531999999999</v>
+        <v>9789.5319999999992</v>
       </c>
       <c r="I14">
         <v>132612389.522</v>
@@ -1038,10 +1067,10 @@
         <v>122631310.954</v>
       </c>
       <c r="K14">
-        <v>142713020.186</v>
+        <v>142713020.18599999</v>
       </c>
       <c r="L14">
-        <v>1207868691.837</v>
+        <v>1207868691.8369999</v>
       </c>
       <c r="M14">
         <v>1114855115.658</v>
@@ -1050,40 +1079,36 @@
         <v>1302097491.55</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>6622.005</v>
+        <v>6622.0050000000001</v>
       </c>
       <c r="D15">
-        <v>6127.231</v>
+        <v>6127.2309999999998</v>
       </c>
       <c r="E15">
-        <v>7127.814</v>
+        <v>7127.8140000000003</v>
       </c>
       <c r="F15">
-        <v>7543.314</v>
+        <v>7543.3140000000003</v>
       </c>
       <c r="G15">
-        <v>6963.935</v>
+        <v>6963.9350000000004</v>
       </c>
       <c r="H15">
-        <v>8136.022</v>
+        <v>8136.0219999999999</v>
       </c>
       <c r="I15">
         <v>110230198.529</v>
       </c>
       <c r="J15">
-        <v>101951060.666</v>
+        <v>101951060.66599999</v>
       </c>
       <c r="K15">
         <v>118624443.985</v>
@@ -1092,43 +1117,39 @@
         <v>1003178089.908</v>
       </c>
       <c r="M15">
-        <v>926044819.365</v>
+        <v>926044819.36500001</v>
       </c>
       <c r="N15">
         <v>1082515638.592</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>8396.795</v>
+        <v>8396.7950000000001</v>
       </c>
       <c r="D16">
-        <v>7775.929</v>
+        <v>7775.9290000000001</v>
       </c>
       <c r="E16">
-        <v>9023.387000000001</v>
+        <v>9023.3870000000006</v>
       </c>
       <c r="F16">
-        <v>9595.795</v>
+        <v>9595.7950000000001</v>
       </c>
       <c r="G16">
-        <v>8870.436</v>
+        <v>8870.4359999999997</v>
       </c>
       <c r="H16">
         <v>10332.776</v>
       </c>
       <c r="I16">
-        <v>139812873.545</v>
+        <v>139812873.54499999</v>
       </c>
       <c r="J16">
         <v>129458099.404</v>
@@ -1143,34 +1164,30 @@
         <v>1180085815.914</v>
       </c>
       <c r="N16">
-        <v>1374305021.307</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>1374305021.3069999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>55990.867</v>
+        <v>55990.866999999998</v>
       </c>
       <c r="D17">
         <v>53171.19</v>
       </c>
       <c r="E17">
-        <v>58829.584</v>
+        <v>58829.584000000003</v>
       </c>
       <c r="F17">
         <v>18470.001</v>
       </c>
       <c r="G17">
-        <v>17212.792</v>
+        <v>17212.792000000001</v>
       </c>
       <c r="H17">
         <v>19744.413</v>
@@ -1188,37 +1205,33 @@
         <v>2456836665.638</v>
       </c>
       <c r="M17">
-        <v>2288770300.347</v>
+        <v>2288770300.3470001</v>
       </c>
       <c r="N17">
-        <v>2626444184.343</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>2626444184.3429999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
         <v>47378.248</v>
       </c>
       <c r="D18">
-        <v>45104.185</v>
+        <v>45104.184999999998</v>
       </c>
       <c r="E18">
         <v>49640.39</v>
       </c>
       <c r="F18">
-        <v>15828.167</v>
+        <v>15828.166999999999</v>
       </c>
       <c r="G18">
-        <v>14848.809</v>
+        <v>14848.808999999999</v>
       </c>
       <c r="H18">
         <v>16807.678</v>
@@ -1239,34 +1252,30 @@
         <v>1975755839.026</v>
       </c>
       <c r="N18">
-        <v>2235837863.468</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>2235837863.4679999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>91940.137</v>
+        <v>91940.137000000002</v>
       </c>
       <c r="D19">
-        <v>87865.107</v>
+        <v>87865.107000000004</v>
       </c>
       <c r="E19">
-        <v>96036.04700000001</v>
+        <v>96036.047000000006</v>
       </c>
       <c r="F19">
         <v>36427.248</v>
       </c>
       <c r="G19">
-        <v>34362.541</v>
+        <v>34362.540999999997</v>
       </c>
       <c r="H19">
         <v>38500.733</v>
@@ -1281,28 +1290,24 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>4844719266.443</v>
+        <v>4844719266.4429998</v>
       </c>
       <c r="M19">
-        <v>4572938335.861</v>
+        <v>4572938335.8610001</v>
       </c>
       <c r="N19">
-        <v>5120144777.643</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>5120144777.6429996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>13719.621</v>
+        <v>13719.620999999999</v>
       </c>
       <c r="D20">
         <v>12823.294</v>
@@ -1314,49 +1319,45 @@
         <v>6390.62</v>
       </c>
       <c r="G20">
-        <v>5997.898999999999</v>
+        <v>5997.8989999999994</v>
       </c>
       <c r="H20">
-        <v>6796.111000000001</v>
+        <v>6796.1110000000008</v>
       </c>
       <c r="I20">
-        <v>402217054.99</v>
+        <v>402217054.99000001</v>
       </c>
       <c r="J20">
-        <v>375932673.099</v>
+        <v>375932673.09899998</v>
       </c>
       <c r="K20">
-        <v>429538237.406</v>
+        <v>429538237.40600002</v>
       </c>
       <c r="L20">
-        <v>849829141.99</v>
+        <v>849829141.99000001</v>
       </c>
       <c r="M20">
-        <v>797632686.747</v>
+        <v>797632686.74699998</v>
       </c>
       <c r="N20">
         <v>903786276.875</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>67289.84299999999</v>
+        <v>67289.842999999993</v>
       </c>
       <c r="D21">
-        <v>63612.838</v>
+        <v>63612.838000000003</v>
       </c>
       <c r="E21">
-        <v>71004.99400000001</v>
+        <v>71004.994000000006</v>
       </c>
       <c r="F21">
         <v>91363.5</v>
@@ -1365,49 +1366,45 @@
         <v>86759.841</v>
       </c>
       <c r="H21">
-        <v>96009.371</v>
+        <v>96009.370999999999</v>
       </c>
       <c r="I21">
         <v>3546376890.612</v>
       </c>
       <c r="J21">
-        <v>3352182819.897</v>
+        <v>3352182819.8969998</v>
       </c>
       <c r="K21">
-        <v>3742391389.699</v>
+        <v>3742391389.6989999</v>
       </c>
       <c r="L21">
-        <v>12151893477.422</v>
+        <v>12151893477.422001</v>
       </c>
       <c r="M21">
-        <v>11541793386.412</v>
+        <v>11541793386.412001</v>
       </c>
       <c r="N21">
         <v>12768013616.247</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>22983.611</v>
+        <v>22983.611000000001</v>
       </c>
       <c r="D22">
-        <v>21267.497</v>
+        <v>21267.496999999999</v>
       </c>
       <c r="E22">
-        <v>24723.825</v>
+        <v>24723.825000000001</v>
       </c>
       <c r="F22">
-        <v>26221.737</v>
+        <v>26221.737000000001</v>
       </c>
       <c r="G22">
         <v>24218.981</v>
@@ -1416,52 +1413,48 @@
         <v>28258.33</v>
       </c>
       <c r="I22">
-        <v>382655461.596</v>
+        <v>382655461.59600002</v>
       </c>
       <c r="J22">
-        <v>354040471.024</v>
+        <v>354040471.02399999</v>
       </c>
       <c r="K22">
-        <v>411659242.641</v>
+        <v>411659242.64099997</v>
       </c>
       <c r="L22">
-        <v>3487331788.179</v>
+        <v>3487331788.1789999</v>
       </c>
       <c r="M22">
-        <v>3220985750.937</v>
+        <v>3220985750.9369998</v>
       </c>
       <c r="N22">
-        <v>3758918151.449</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>3758918151.4489999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>195309.252</v>
+        <v>195309.25200000001</v>
       </c>
       <c r="D23">
-        <v>186140.482</v>
+        <v>186140.48199999999</v>
       </c>
       <c r="E23">
-        <v>204506.021</v>
+        <v>204506.02100000001</v>
       </c>
       <c r="F23">
-        <v>70725.416</v>
+        <v>70725.415999999997</v>
       </c>
       <c r="G23">
-        <v>66424.14199999999</v>
+        <v>66424.141999999993</v>
       </c>
       <c r="H23">
-        <v>75052.82399999999</v>
+        <v>75052.823999999993</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1473,76 +1466,68 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>9406988758.469</v>
+        <v>9406988758.4689999</v>
       </c>
       <c r="M23">
-        <v>8837464475.234001</v>
+        <v>8837464475.2340012</v>
       </c>
       <c r="N23">
-        <v>9982426825.453999</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>9982426825.4539986</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>9179.758</v>
+        <v>9179.7579999999998</v>
       </c>
       <c r="D24">
-        <v>8670.005999999999</v>
+        <v>8670.0059999999994</v>
       </c>
       <c r="E24">
-        <v>9701.429</v>
+        <v>9701.4290000000001</v>
       </c>
       <c r="F24">
         <v>17093.266</v>
       </c>
       <c r="G24">
-        <v>16088.138</v>
+        <v>16088.138000000001</v>
       </c>
       <c r="H24">
         <v>18142.7</v>
       </c>
       <c r="I24">
-        <v>359859983.438</v>
+        <v>359859983.43800002</v>
       </c>
       <c r="J24">
-        <v>339900737.424</v>
+        <v>339900737.42400002</v>
       </c>
       <c r="K24">
-        <v>380314926.985</v>
+        <v>380314926.98500001</v>
       </c>
       <c r="L24">
-        <v>2273423847.701</v>
+        <v>2273423847.7010002</v>
       </c>
       <c r="M24">
-        <v>2139171114.416</v>
+        <v>2139171114.4159999</v>
       </c>
       <c r="N24">
-        <v>2412513604.999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>2412513604.9990001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>107934.032</v>
+        <v>107934.03200000001</v>
       </c>
       <c r="D25">
         <v>100964.534</v>
@@ -1551,13 +1536,13 @@
         <v>114878.933</v>
       </c>
       <c r="F25">
-        <v>1087079.874</v>
+        <v>1087079.8740000001</v>
       </c>
       <c r="G25">
         <v>1044616.865</v>
       </c>
       <c r="H25">
-        <v>1129563.021</v>
+        <v>1129563.0209999999</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1569,43 +1554,39 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>144588786837.826</v>
+        <v>144588786837.82599</v>
       </c>
       <c r="M25">
-        <v>138918235953.446</v>
+        <v>138918235953.44601</v>
       </c>
       <c r="N25">
-        <v>150273400287.674</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>150273400287.67401</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>129648.903</v>
+        <v>129648.90300000001</v>
       </c>
       <c r="D26">
-        <v>121935.225</v>
+        <v>121935.22500000001</v>
       </c>
       <c r="E26">
         <v>137418.35</v>
       </c>
       <c r="F26">
-        <v>396720.737</v>
+        <v>396720.73700000002</v>
       </c>
       <c r="G26">
-        <v>378437.382</v>
+        <v>378437.38199999998</v>
       </c>
       <c r="H26">
-        <v>415099.454</v>
+        <v>415099.45400000003</v>
       </c>
       <c r="I26">
         <v>1567972182.927</v>
@@ -1614,28 +1595,24 @@
         <v>1473120595.23</v>
       </c>
       <c r="K26">
-        <v>1664038997.074</v>
+        <v>1664038997.0739999</v>
       </c>
       <c r="L26">
-        <v>52764957411.97501</v>
+        <v>52764957411.975014</v>
       </c>
       <c r="M26">
-        <v>50323599341.15601</v>
+        <v>50323599341.156013</v>
       </c>
       <c r="N26">
-        <v>55208331138.22701</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>55208331138.227013</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
       </c>
       <c r="C27">
         <v>113980.462</v>
@@ -1647,172 +1624,160 @@
         <v>120327.787</v>
       </c>
       <c r="F27">
-        <v>391503.291</v>
+        <v>391503.29100000003</v>
       </c>
       <c r="G27">
-        <v>375362.1800000001</v>
+        <v>375362.18000000011</v>
       </c>
       <c r="H27">
-        <v>407675.156</v>
+        <v>407675.15600000002</v>
       </c>
       <c r="I27">
         <v>1360942103.05</v>
       </c>
       <c r="J27">
-        <v>1283071925.284</v>
+        <v>1283071925.2839999</v>
       </c>
       <c r="K27">
-        <v>1440338356.186</v>
+        <v>1440338356.1860001</v>
       </c>
       <c r="L27">
-        <v>52068000931.605</v>
+        <v>52068000931.605003</v>
       </c>
       <c r="M27">
-        <v>49916275105.32999</v>
+        <v>49916275105.329987</v>
       </c>
       <c r="N27">
-        <v>54240278974.492</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>54240278974.491997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>172786.752</v>
+        <v>172786.75200000001</v>
       </c>
       <c r="D28">
-        <v>163889.338</v>
+        <v>163889.33799999999</v>
       </c>
       <c r="E28">
-        <v>181718.175</v>
+        <v>181718.17499999999</v>
       </c>
       <c r="F28">
-        <v>510650.385</v>
+        <v>510650.38500000001</v>
       </c>
       <c r="G28">
         <v>490306.304</v>
       </c>
       <c r="H28">
-        <v>531047.747</v>
+        <v>531047.74699999997</v>
       </c>
       <c r="I28">
-        <v>1762195104.659</v>
+        <v>1762195104.6589999</v>
       </c>
       <c r="J28">
-        <v>1665864180.93</v>
+        <v>1665864180.9300001</v>
       </c>
       <c r="K28">
         <v>1859526443.471</v>
       </c>
       <c r="L28">
-        <v>67925295508.007</v>
+        <v>67925295508.007004</v>
       </c>
       <c r="M28">
-        <v>65215408920.70599</v>
+        <v>65215408920.705994</v>
       </c>
       <c r="N28">
-        <v>70650448649.979</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>70650448649.979004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>416416.117</v>
+        <v>416416.11700000003</v>
       </c>
       <c r="D29">
-        <v>393478.651</v>
+        <v>393478.65100000001</v>
       </c>
       <c r="E29">
-        <v>439464.312</v>
+        <v>439464.31199999998</v>
       </c>
       <c r="F29">
         <v>1298874.412999999</v>
       </c>
       <c r="G29">
-        <v>1244105.866</v>
+        <v>1244105.8659999999</v>
       </c>
       <c r="H29">
-        <v>1353822.357</v>
+        <v>1353822.3570000001</v>
       </c>
       <c r="I29">
-        <v>4691109390.636002</v>
+        <v>4691109390.6360016</v>
       </c>
       <c r="J29">
-        <v>4422056701.443999</v>
+        <v>4422056701.4439993</v>
       </c>
       <c r="K29">
-        <v>4963903796.731001</v>
+        <v>4963903796.7310009</v>
       </c>
       <c r="L29">
-        <v>172758253851.587</v>
+        <v>172758253851.58701</v>
       </c>
       <c r="M29">
-        <v>165455283367.192</v>
+        <v>165455283367.19199</v>
       </c>
       <c r="N29">
         <v>180099058762.698</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Chronic diseases</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
       </c>
       <c r="C30">
         <v>113172.833</v>
       </c>
       <c r="D30">
-        <v>106373.635</v>
+        <v>106373.63499999999</v>
       </c>
       <c r="E30">
-        <v>120079.358</v>
+        <v>120079.35799999999</v>
       </c>
       <c r="F30">
-        <v>141069.123</v>
+        <v>141069.12299999999</v>
       </c>
       <c r="G30">
         <v>133064.859</v>
       </c>
       <c r="H30">
-        <v>149206.512</v>
+        <v>149206.51199999999</v>
       </c>
       <c r="I30">
-        <v>4691109390.636002</v>
+        <v>4691109390.6360016</v>
       </c>
       <c r="J30">
-        <v>4422056701.443999</v>
+        <v>4422056701.4439993</v>
       </c>
       <c r="K30">
-        <v>4963903796.731001</v>
+        <v>4963903796.7310009</v>
       </c>
       <c r="L30">
         <v>18762478255.292</v>
       </c>
       <c r="M30">
-        <v>17699582938.512</v>
+        <v>17699582938.512001</v>
       </c>
       <c r="N30">
         <v>19843231649.57</v>
